--- a/Python/Codewars/codewars.xlsx
+++ b/Python/Codewars/codewars.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>№</t>
   </si>
@@ -79,6 +79,33 @@
   </si>
   <si>
     <t>isinstance()</t>
+  </si>
+  <si>
+    <t>capitalize()</t>
+  </si>
+  <si>
+    <t>метод</t>
+  </si>
+  <si>
+    <t>enumerate()</t>
+  </si>
+  <si>
+    <t>Принимает последовательность и 2-ым аргументом может принимать начальный индекс</t>
+  </si>
+  <si>
+    <t>title()</t>
+  </si>
+  <si>
+    <t>set()</t>
+  </si>
+  <si>
+    <t>list()</t>
+  </si>
+  <si>
+    <t>count()</t>
+  </si>
+  <si>
+    <t>Метод для коллекций и строк, принимает значение, которое нужно посчитать</t>
   </si>
 </sst>
 </file>
@@ -466,14 +493,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E1:H17"/>
+  <dimension ref="E1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1"/>
     <col min="5" max="5" width="6.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="42.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="53.42578125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -653,25 +680,125 @@
       <c r="E15" s="3">
         <v>14</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" s="3">
         <v>15</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E17" s="3">
         <v>16</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="3">
+        <v>17</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="3">
+        <v>18</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="3">
+        <v>19</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="3"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="3"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="3"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="3"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="3"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="5:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="3"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="5:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="3"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
